--- a/evaluation_surveys/008_simple_instructor_evaluation_form_template--evaluation_surveys.xlsx
+++ b/evaluation_surveys/008_simple_instructor_evaluation_form_template--evaluation_surveys.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>instructor</t>
+          <t>instructor_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Instructor</t>
+          <t>Instructor 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>professor</t>
+          <t>professor_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Professor 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>evaluation_date</t>
+          <t>evaluation_date_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Evaluation Date</t>
+          <t>Evaluation Date 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
